--- a/Scripts/DRT.xlsx
+++ b/Scripts/DRT.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kritim\Downloads\Scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kritim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C289FF6-0785-4BCB-9709-99BBDCEBA3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F9C975-422D-4092-B538-F1BF5A9731B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F913FD20-BF5B-4473-8D33-B1EBD8683930}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{4ABB9162-0518-A94E-B565-C9D38D89998E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +35,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+  <si>
+    <t>a'</t>
+  </si>
+  <si>
+    <t>a"</t>
+  </si>
   <si>
     <t>SCF</t>
   </si>
@@ -89,45 +94,27 @@
     <t>Symmetry</t>
   </si>
   <si>
-    <t>4,6-pyrimidine C2V</t>
-  </si>
-  <si>
-    <t>CAS(6,4)</t>
-  </si>
-  <si>
-    <t>a1</t>
-  </si>
-  <si>
-    <t>b1</t>
-  </si>
-  <si>
-    <t>b2</t>
-  </si>
-  <si>
-    <t>a2</t>
-  </si>
-  <si>
-    <t>B2 (3)</t>
-  </si>
-  <si>
-    <t>Number of unique electrons</t>
-  </si>
-  <si>
-    <t>Signlet</t>
-  </si>
-  <si>
-    <t>A1 (1)</t>
+    <t>A' (1)</t>
+  </si>
+  <si>
+    <t>Singlet</t>
+  </si>
+  <si>
+    <t>2,4-thiazole Cs</t>
+  </si>
+  <si>
+    <t>CAS(10,8)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -137,20 +124,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -267,34 +243,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -303,27 +289,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -342,9 +307,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -352,39 +317,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -436,7 +401,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -488,7 +453,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -547,6 +512,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -555,13 +527,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -626,54 +591,34 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0108E1EA-761A-43EF-9138-C3C08891529E}">
-  <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8C0C948-468F-8F4B-B850-580232A05243}">
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -684,240 +629,188 @@
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>22</v>
-      </c>
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7">
+        <v>16</v>
+      </c>
+      <c r="D4" s="7">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="9">
+        <v>2</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="7">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="4">
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="9">
+        <v>3</v>
+      </c>
+      <c r="D8" s="9">
+        <v>5</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="4">
-        <v>6</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="C10" s="7">
+        <v>8</v>
+      </c>
+      <c r="D10" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
-        <v>1</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="9"/>
+      <c r="B12" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4">
-        <v>9</v>
-      </c>
-      <c r="D6" s="4">
-        <v>2</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="C12" s="9">
+        <v>7</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="9"/>
+      <c r="B13" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="9">
+        <v>3</v>
+      </c>
+      <c r="D13" s="9">
         <v>5</v>
       </c>
-      <c r="F6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7" t="s">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="11">
+        <v>10</v>
+      </c>
+      <c r="D15" s="11">
         <v>5</v>
       </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>2</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="4">
-        <v>4</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
-        <v>2</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6">
-        <v>5</v>
-      </c>
-      <c r="D12" s="6">
-        <v>2</v>
-      </c>
-      <c r="E12" s="6">
-        <v>3</v>
-      </c>
-      <c r="F12" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="6">
-        <v>2</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6">
-        <v>2</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="8">
-        <v>7</v>
-      </c>
-      <c r="D15" s="8">
-        <v>2</v>
-      </c>
-      <c r="E15" s="8">
-        <v>5</v>
-      </c>
-      <c r="F15" s="8">
-        <v>1</v>
-      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
@@ -927,110 +820,121 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="15" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="9">
+        <v>1</v>
+      </c>
+      <c r="B19" s="14">
+        <v>3</v>
+      </c>
+      <c r="C19" s="14">
+        <v>42</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="B24" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="20"/>
-      <c r="G18" s="21"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
+      <c r="C24" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="9">
         <v>1</v>
       </c>
-      <c r="B19" s="16">
-        <v>3</v>
-      </c>
-      <c r="C19" s="16">
-        <v>40</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="2">
-        <v>3</v>
-      </c>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
+      <c r="B25" s="14">
         <v>1</v>
       </c>
-      <c r="B24" s="19">
-        <v>1</v>
-      </c>
-      <c r="C24" s="19">
-        <v>40</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="2">
-        <v>3</v>
-      </c>
+      <c r="C25" s="14">
+        <v>42</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
